--- a/branches/dev/v2027/ValueSet-mii-vs-patho-container-type-snomed-ct.xlsx
+++ b/branches/dev/v2027/ValueSet-mii-vs-patho-container-type-snomed-ct.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T13:18:58+00:00</t>
+    <t>2026-09-01T13:59:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/v2027/ValueSet-mii-vs-patho-container-type-snomed-ct.xlsx
+++ b/branches/dev/v2027/ValueSet-mii-vs-patho-container-type-snomed-ct.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc</t>
+    <t>2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T13:59:06+00:00</t>
+    <t>2026-09-03T08:45:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/v2027/ValueSet-mii-vs-patho-container-type-snomed-ct.xlsx
+++ b/branches/dev/v2027/ValueSet-mii-vs-patho-container-type-snomed-ct.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc1</t>
+    <t>2027.0.0-ballot.rc2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T08:45:38+00:00</t>
+    <t>2026-09-08T11:58:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/v2027/ValueSet-mii-vs-patho-container-type-snomed-ct.xlsx
+++ b/branches/dev/v2027/ValueSet-mii-vs-patho-container-type-snomed-ct.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T11:58:20+00:00</t>
+    <t>2026-09-08T12:58:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -102,61 +102,61 @@
     <t>434746001</t>
   </si>
   <si>
-    <t>Specimen vial (physical object)</t>
+    <t>Specimen vial</t>
   </si>
   <si>
     <t>434464009</t>
   </si>
   <si>
-    <t>Tissue cassette (physical object)</t>
+    <t>Tissue cassette</t>
   </si>
   <si>
     <t>434708008</t>
   </si>
   <si>
-    <t>Tissue cassette for microarray (physical object)</t>
+    <t>Tissue cassette for microarray</t>
   </si>
   <si>
     <t>433466003</t>
   </si>
   <si>
-    <t>Microscope slide (physical object)</t>
+    <t>Microscope slide</t>
   </si>
   <si>
     <t>433453003</t>
   </si>
   <si>
-    <t>Specimen container component (physical object)</t>
+    <t>Specimen container component</t>
   </si>
   <si>
     <t>434533009</t>
   </si>
   <si>
-    <t>Electron microscopy grid (physical object)</t>
+    <t>Electron microscopy grid</t>
   </si>
   <si>
     <t>434822004</t>
   </si>
   <si>
-    <t>Specimen well (physical object)</t>
+    <t>Specimen well</t>
   </si>
   <si>
     <t>433472003</t>
   </si>
   <si>
-    <t>Microscope slide coverslip (physical object)</t>
+    <t>Microscope slide coverslip</t>
   </si>
   <si>
     <t>434473001</t>
   </si>
   <si>
-    <t>Specimen container lid (physical object)</t>
+    <t>Specimen container lid</t>
   </si>
   <si>
     <t>706053007</t>
   </si>
   <si>
-    <t>General specimen container (physical object)</t>
+    <t>General specimen container</t>
   </si>
   <si>
     <t/>

--- a/branches/dev/v2027/ValueSet-mii-vs-patho-container-type-snomed-ct.xlsx
+++ b/branches/dev/v2027/ValueSet-mii-vs-patho-container-type-snomed-ct.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T12:58:28+00:00</t>
+    <t>2026-09-08T14:07:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/v2027/ValueSet-mii-vs-patho-container-type-snomed-ct.xlsx
+++ b/branches/dev/v2027/ValueSet-mii-vs-patho-container-type-snomed-ct.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T14:07:59+00:00</t>
+    <t>2026-09-08T14:30:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
